--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_161_R17.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_161_R17.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5974</v>
+        <v>4.3683</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0659</v>
+        <v>4.6688</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4684</v>
+        <v>-0.3004</v>
       </c>
       <c r="G2" t="n">
         <v>1.2218</v>
@@ -610,13 +610,13 @@
         <v>1.3917</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3756</v>
+        <v>0.1465</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8417</v>
+        <v>0.4446</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4661</v>
+        <v>-0.2981</v>
       </c>
       <c r="V2" t="n">
         <v>1.6083</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0107</v>
+        <v>1.0434</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1977</v>
+        <v>1.2916</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2083</v>
+        <v>-0.2481</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.6848</v>
+        <v>1.9717</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.6973</v>
+        <v>2.5138</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.9875</v>
+        <v>-0.542</v>
       </c>
       <c r="J3" t="n">
-        <v>-3.0555</v>
+        <v>2.9798</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.7036</v>
+        <v>2.6755</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3519</v>
+        <v>0.3044</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6293</v>
+        <v>-1.0081</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0063</v>
+        <v>-0.1617</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.8464</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8556</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1619</v>
+        <v>-0.3047</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1799</v>
+        <v>-0.3534</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.018</v>
+        <v>0.0488</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6778999999999999</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1332</v>
+        <v>-0.0638</v>
       </c>
       <c r="E4" t="n">
-        <v>0.3165</v>
+        <v>-1.0532</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.4498</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9717</v>
+        <v>-3.2091</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5138</v>
+        <v>-3.5703</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.542</v>
+        <v>0.3611</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9798</v>
+        <v>-1.6973</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6755</v>
+        <v>-3.2728</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3044</v>
+        <v>1.5756</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.0081</v>
+        <v>-1.5119</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1617</v>
+        <v>-0.2974</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.8464</v>
+        <v>-1.2144</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.4813</v>
+        <v>-0.4088</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.3285</v>
+        <v>-0.4281</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1529</v>
+        <v>0.0193</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5361</v>
+        <v>1.4665</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6083</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.1733</v>
+        <v>-0.6156</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0282</v>
+        <v>-1.9919</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8549</v>
+        <v>1.3764</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.2091</v>
+        <v>-3.6848</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.5703</v>
+        <v>-1.6973</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3611</v>
+        <v>-1.9875</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.6973</v>
+        <v>-3.0555</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.2728</v>
+        <v>-1.7036</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5756</v>
+        <v>-1.3519</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.5119</v>
+        <v>-0.6293</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2974</v>
+        <v>0.0063</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2144</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.5182</v>
+        <v>0.5357</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4031</v>
+        <v>0.3857</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1151</v>
+        <v>0.15</v>
       </c>
       <c r="V5" t="n">
-        <v>1.4665</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5003</v>
+        <v>-1.7371</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.643</v>
+        <v>-1.3757</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1427</v>
+        <v>-0.3614</v>
       </c>
       <c r="G6" t="n">
         <v>-2.0525</v>
@@ -922,13 +922,13 @@
         <v>0.6959</v>
       </c>
       <c r="S6" t="n">
-        <v>1.0161</v>
+        <v>0.7793</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4323</v>
+        <v>-0.165</v>
       </c>
       <c r="U6" t="n">
-        <v>1.4484</v>
+        <v>0.9443</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4104</v>
+        <v>-2.5202</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8369</v>
+        <v>-0.6443</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5735</v>
+        <v>-1.8759</v>
       </c>
       <c r="G7" t="n">
         <v>-2.5872</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5531</v>
+        <v>0.4433</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2082</v>
+        <v>-0.0156</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7613</v>
+        <v>0.4589</v>
       </c>
       <c r="V7" t="n">
         <v>-1.0722</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.0631</v>
+        <v>-2.6277</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7967</v>
+        <v>-1.5294</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2663</v>
+        <v>-1.0983</v>
       </c>
       <c r="G8" t="n">
         <v>0.2236</v>
@@ -1078,13 +1078,13 @@
         <v>1.1598</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3677</v>
+        <v>0.803</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0633</v>
+        <v>0.3306</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3044</v>
+        <v>0.4725</v>
       </c>
       <c r="V8" t="n">
         <v>2.1444</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.6787</v>
+        <v>-3.318</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1285</v>
+        <v>-1.9359</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5502</v>
+        <v>-1.3821</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8041</v>
@@ -1156,13 +1156,13 @@
         <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0532</v>
+        <v>0.4138</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0589</v>
+        <v>0.1338</v>
       </c>
       <c r="U9" t="n">
-        <v>0.112</v>
+        <v>0.2801</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-6.3988</v>
+        <v>-7.1588</v>
       </c>
       <c r="E10" t="n">
-        <v>-5.9337</v>
+        <v>-6.492</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4652</v>
+        <v>-0.6667999999999999</v>
       </c>
       <c r="G10" t="n">
         <v>-6.9865</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1237</v>
+        <v>0.3637</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3268</v>
+        <v>-0.2315</v>
       </c>
       <c r="U10" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.5953000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-13.7497</v>
+        <v>-12.6295</v>
       </c>
       <c r="E11" t="n">
-        <v>-10.1823</v>
+        <v>-9.062000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5675</v>
+        <v>-3.5672</v>
       </c>
       <c r="G11" t="n">
         <v>-17.9071</v>
@@ -1288,7 +1288,7 @@
         <v>-3.3418</v>
       </c>
       <c r="K11" t="n">
-        <v>-3.909400000000001</v>
+        <v>-3.9094</v>
       </c>
       <c r="L11" t="n">
         <v>0.5677999999999995</v>
@@ -1312,13 +1312,13 @@
         <v>12.7575</v>
       </c>
       <c r="S11" t="n">
-        <v>1.651799999999999</v>
+        <v>2.7718</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.019300000000001</v>
+        <v>0.1011000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>2.6709</v>
+        <v>2.6711</v>
       </c>
       <c r="V11" t="n">
         <v>4.8249</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.2157</v>
+        <v>7.8447</v>
       </c>
       <c r="E12" t="n">
         <v>7.7269</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5112</v>
+        <v>0.1179</v>
       </c>
       <c r="G12" t="n">
         <v>7.0717</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1756</v>
+        <v>-0.5465</v>
       </c>
       <c r="T12" t="n">
         <v>-0.6563</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5192</v>
+        <v>0.1098</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.5905</v>
+        <v>4.6583</v>
       </c>
       <c r="E13" t="n">
-        <v>1.6913</v>
+        <v>1.4554</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8992</v>
+        <v>3.2029</v>
       </c>
       <c r="G13" t="n">
         <v>1.4168</v>
@@ -1468,13 +1468,13 @@
         <v>2.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3361</v>
+        <v>0.4039</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0633</v>
+        <v>-0.1727</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2728</v>
+        <v>0.5766</v>
       </c>
       <c r="V13" t="n">
         <v>1.214</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>N. MELLI</t>
+          <t>B. BOSTON JR.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0698</v>
+        <v>3.5033</v>
       </c>
       <c r="E14" t="n">
-        <v>0.73</v>
+        <v>2.3689</v>
       </c>
       <c r="F14" t="n">
-        <v>3.3398</v>
+        <v>1.1344</v>
       </c>
       <c r="G14" t="n">
-        <v>3.2031</v>
+        <v>1.2502</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4731</v>
+        <v>0.4873</v>
       </c>
       <c r="I14" t="n">
-        <v>1.73</v>
+        <v>0.7629</v>
       </c>
       <c r="J14" t="n">
-        <v>1.6772</v>
+        <v>1.1928</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9411</v>
+        <v>0.3732</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7361</v>
+        <v>0.8196</v>
       </c>
       <c r="M14" t="n">
-        <v>1.5259</v>
+        <v>0.0574</v>
       </c>
       <c r="N14" t="n">
-        <v>0.5321</v>
+        <v>0.1141</v>
       </c>
       <c r="O14" t="n">
-        <v>0.9939</v>
+        <v>-0.0568</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7792</v>
+        <v>0.3253</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2126</v>
+        <v>-0.4323</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5666</v>
+        <v>0.7576000000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.6083</v>
+        <v>0.5361</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. BOSTON JR.</t>
+          <t>T. BIBEROVIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2681</v>
+        <v>3.4803</v>
       </c>
       <c r="E15" t="n">
-        <v>2.3689</v>
+        <v>0.2081</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8992</v>
+        <v>3.2722</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2502</v>
+        <v>5.0785</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4873</v>
+        <v>-0.2315</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7629</v>
+        <v>5.31</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1928</v>
+        <v>2.9451</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3732</v>
+        <v>-1.371</v>
       </c>
       <c r="L15" t="n">
-        <v>0.8196</v>
+        <v>4.3161</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0574</v>
+        <v>2.1334</v>
       </c>
       <c r="N15" t="n">
-        <v>0.1141</v>
+        <v>1.1396</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0568</v>
+        <v>0.9939</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3917</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0901</v>
+        <v>0.2574</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4323</v>
+        <v>-0.3299</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5223</v>
+        <v>0.5874</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6083</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
         <v>-1.0722</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. BIBEROVIC</t>
+          <t>N. MELLI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.571</v>
+        <v>3.4699</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0278</v>
+        <v>0.3762</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5988</v>
+        <v>3.0938</v>
       </c>
       <c r="G16" t="n">
-        <v>5.0785</v>
+        <v>3.2031</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2315</v>
+        <v>1.4731</v>
       </c>
       <c r="I16" t="n">
-        <v>5.31</v>
+        <v>1.73</v>
       </c>
       <c r="J16" t="n">
-        <v>2.9451</v>
+        <v>1.6772</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.371</v>
+        <v>0.9411</v>
       </c>
       <c r="L16" t="n">
-        <v>4.3161</v>
+        <v>0.7361</v>
       </c>
       <c r="M16" t="n">
-        <v>2.1334</v>
+        <v>1.5259</v>
       </c>
       <c r="N16" t="n">
-        <v>1.1396</v>
+        <v>0.5321</v>
       </c>
       <c r="O16" t="n">
         <v>0.9939</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.8556</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6519</v>
+        <v>1.1793</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5658</v>
+        <v>-0.1412</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0861</v>
+        <v>1.3205</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.0722</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1403</v>
+        <v>0.5446</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.0355</v>
+        <v>0.2004</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1048</v>
+        <v>0.3441</v>
       </c>
       <c r="G17" t="n">
         <v>1.0538</v>
@@ -1780,13 +1780,13 @@
         <v>1.3917</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2996</v>
+        <v>0.3853</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4244</v>
+        <v>-0.1885</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1248</v>
+        <v>0.5737</v>
       </c>
       <c r="V17" t="n">
         <v>-2.2862</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.5597</v>
+        <v>-0.4862</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5929</v>
+        <v>-0.4749</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0332</v>
+        <v>-0.0112</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7161</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1564</v>
+        <v>0.23</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0158</v>
+        <v>0.1338</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1406</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.8558</v>
+        <v>-1.4905</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6395999999999999</v>
+        <v>-0.5217000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2162</v>
+        <v>-0.9689</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0246</v>
@@ -1936,13 +1936,13 @@
         <v>0.232</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0631</v>
+        <v>-0.6978</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3655</v>
+        <v>-0.2475</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6976</v>
+        <v>-0.4503</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. BALDWIN IV</t>
+          <t>D. HALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6183</v>
+        <v>-1.6858</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7199</v>
+        <v>-5.58</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.8984</v>
+        <v>3.8942</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8137</v>
+        <v>-0.2401</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4109</v>
+        <v>0.4693</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2246</v>
+        <v>-0.7093</v>
       </c>
       <c r="J20" t="n">
-        <v>1.6214</v>
+        <v>-1.7983</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4496</v>
+        <v>-0.4097</v>
       </c>
       <c r="L20" t="n">
-        <v>2.071</v>
+        <v>-1.3887</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.8077</v>
+        <v>1.5583</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0387</v>
+        <v>0.8789</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.8464</v>
+        <v>0.6793</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6237</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q20" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3361</v>
+        <v>-0.054</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1379</v>
+        <v>-0.3025</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1981</v>
+        <v>0.2484</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. HALL</t>
+          <t>W. BALDWIN IV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.7911</v>
+        <v>-2.9436</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.9339</v>
+        <v>-2.1917</v>
       </c>
       <c r="F21" t="n">
-        <v>3.1428</v>
+        <v>-0.7519</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2401</v>
+        <v>0.8137</v>
       </c>
       <c r="H21" t="n">
-        <v>0.4693</v>
+        <v>-0.4109</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7093</v>
+        <v>1.2246</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.7983</v>
+        <v>1.6214</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4097</v>
+        <v>-0.4496</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3887</v>
+        <v>2.071</v>
       </c>
       <c r="M21" t="n">
-        <v>1.5583</v>
+        <v>-0.8077</v>
       </c>
       <c r="N21" t="n">
-        <v>0.8789</v>
+        <v>0.0387</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6793</v>
+        <v>-0.8464</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3917</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q21" t="n">
         <v>-3.4793</v>
       </c>
       <c r="R21" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1593</v>
+        <v>0.0108</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6563</v>
+        <v>-0.3339</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.503</v>
+        <v>0.3446</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="22">
@@ -2125,19 +2125,19 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>13.7499</v>
+        <v>16.895</v>
       </c>
       <c r="E22" t="n">
-        <v>3.5675</v>
+        <v>3.5676</v>
       </c>
       <c r="F22" t="n">
-        <v>10.1824</v>
+        <v>13.3275</v>
       </c>
       <c r="G22" t="n">
         <v>17.907</v>
       </c>
       <c r="H22" t="n">
-        <v>5.8278</v>
+        <v>5.827800000000001</v>
       </c>
       <c r="I22" t="n">
         <v>12.0793</v>
@@ -2146,7 +2146,7 @@
         <v>14.5652</v>
       </c>
       <c r="K22" t="n">
-        <v>1.918299999999999</v>
+        <v>1.9183</v>
       </c>
       <c r="L22" t="n">
         <v>12.6468</v>
@@ -2158,10 +2158,10 @@
         <v>3.9095</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.5678000000000001</v>
+        <v>-0.5678</v>
       </c>
       <c r="P22" t="n">
-        <v>2.319600000000001</v>
+        <v>2.3196</v>
       </c>
       <c r="Q22" t="n">
         <v>-12.7575</v>
@@ -2170,13 +2170,13 @@
         <v>15.0769</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.6516</v>
+        <v>1.4937</v>
       </c>
       <c r="T22" t="n">
         <v>-2.671</v>
       </c>
       <c r="U22" t="n">
-        <v>1.0193</v>
+        <v>4.1645</v>
       </c>
       <c r="V22" t="n">
         <v>-4.8249</v>
